--- a/Team-Data/2007-08/3-21-2007-08.xlsx
+++ b/Team-Data/2007-08/3-21-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
@@ -751,7 +818,7 @@
         <v>19</v>
       </c>
       <c r="AH2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI2" t="n">
         <v>24</v>
@@ -769,10 +836,10 @@
         <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP2" t="n">
         <v>7</v>
@@ -787,13 +854,13 @@
         <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
         <v>15</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>10.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,13 +1003,13 @@
         <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL3" t="n">
         <v>10</v>
@@ -957,7 +1024,7 @@
         <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
         <v>8</v>
@@ -969,13 +1036,13 @@
         <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
@@ -984,13 +1051,13 @@
         <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1124,7 +1191,7 @@
         <v>19</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>16</v>
@@ -1148,7 +1215,7 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
         <v>24</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -1285,19 +1352,19 @@
         <v>-2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF5" t="n">
         <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI5" t="n">
         <v>21</v>
@@ -1318,7 +1385,7 @@
         <v>15</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
         <v>17</v>
@@ -1357,7 +1424,7 @@
         <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F6" t="n">
         <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>0.571</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
@@ -1407,7 +1474,7 @@
         <v>36</v>
       </c>
       <c r="J6" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K6" t="n">
         <v>0.44</v>
@@ -1416,16 +1483,16 @@
         <v>7.1</v>
       </c>
       <c r="M6" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q6" t="n">
         <v>0.72</v>
@@ -1434,10 +1501,10 @@
         <v>13</v>
       </c>
       <c r="S6" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T6" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="U6" t="n">
         <v>19.9</v>
@@ -1446,7 +1513,7 @@
         <v>14.1</v>
       </c>
       <c r="W6" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X6" t="n">
         <v>5</v>
@@ -1455,19 +1522,19 @@
         <v>4.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1497,7 +1564,7 @@
         <v>10</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
         <v>21</v>
@@ -1506,7 +1573,7 @@
         <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR6" t="n">
         <v>3</v>
@@ -1524,7 +1591,7 @@
         <v>9</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
@@ -1661,10 +1728,10 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
@@ -1709,10 +1776,10 @@
         <v>29</v>
       </c>
       <c r="AX7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY7" t="n">
         <v>7</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8</v>
       </c>
       <c r="AZ7" t="n">
         <v>22</v>
@@ -1721,7 +1788,7 @@
         <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -1753,28 +1820,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
         <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>0.594</v>
+        <v>0.588</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
       </c>
       <c r="I8" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="J8" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
       <c r="L8" t="n">
         <v>6.8</v>
@@ -1783,7 +1850,7 @@
         <v>19.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O8" t="n">
         <v>22.9</v>
@@ -1792,28 +1859,28 @@
         <v>30.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.753</v>
+        <v>0.754</v>
       </c>
       <c r="R8" t="n">
         <v>11.5</v>
       </c>
       <c r="S8" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T8" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U8" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V8" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Y8" t="n">
         <v>5</v>
@@ -1825,13 +1892,13 @@
         <v>23.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>109.3</v>
+        <v>109.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -1843,7 +1910,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1852,7 +1919,7 @@
         <v>3</v>
       </c>
       <c r="AK8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL8" t="n">
         <v>13</v>
@@ -1876,7 +1943,7 @@
         <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>4</v>
@@ -1885,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1894,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ8" t="n">
         <v>16</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2025,16 +2092,16 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL9" t="n">
         <v>18</v>
@@ -2043,13 +2110,13 @@
         <v>22</v>
       </c>
       <c r="AN9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
@@ -2070,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2079,10 +2146,10 @@
         <v>3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" t="n">
         <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>0.618</v>
+        <v>0.627</v>
       </c>
       <c r="H10" t="n">
         <v>48.2</v>
@@ -2135,7 +2202,7 @@
         <v>41.4</v>
       </c>
       <c r="J10" t="n">
-        <v>89.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="K10" t="n">
         <v>0.463</v>
@@ -2147,28 +2214,28 @@
         <v>26.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O10" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P10" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q10" t="n">
         <v>0.746</v>
       </c>
       <c r="R10" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S10" t="n">
         <v>30.1</v>
       </c>
       <c r="T10" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U10" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V10" t="n">
         <v>13.2</v>
@@ -2180,10 +2247,10 @@
         <v>4.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA10" t="n">
         <v>21.5</v>
@@ -2192,16 +2259,16 @@
         <v>110.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2225,10 +2292,10 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP10" t="n">
         <v>16</v>
@@ -2237,13 +2304,13 @@
         <v>19</v>
       </c>
       <c r="AR10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
         <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
         <v>8</v>
@@ -2255,13 +2322,13 @@
         <v>2</v>
       </c>
       <c r="AX10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA10" t="n">
         <v>12</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
         <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>0.681</v>
+        <v>0.676</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
@@ -2323,22 +2390,22 @@
         <v>0.45</v>
       </c>
       <c r="L11" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M11" t="n">
         <v>21</v>
       </c>
       <c r="N11" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P11" t="n">
         <v>22.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.721</v>
+        <v>0.719</v>
       </c>
       <c r="R11" t="n">
         <v>12.1</v>
@@ -2353,7 +2420,7 @@
         <v>21.7</v>
       </c>
       <c r="V11" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W11" t="n">
         <v>7.3</v>
@@ -2362,22 +2429,22 @@
         <v>5.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z11" t="n">
         <v>19.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC11" t="n">
         <v>4.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>4</v>
@@ -2389,13 +2456,13 @@
         <v>5</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>15</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>14</v>
       </c>
       <c r="AK11" t="n">
         <v>18</v>
@@ -2416,7 +2483,7 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AR11" t="n">
         <v>9</v>
@@ -2443,7 +2510,7 @@
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12" t="n">
         <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>0.406</v>
+        <v>0.397</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2505,37 +2572,37 @@
         <v>0.442</v>
       </c>
       <c r="L12" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>24.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
       <c r="O12" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P12" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
         <v>31.9</v>
       </c>
       <c r="T12" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U12" t="n">
         <v>22.6</v>
       </c>
       <c r="V12" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W12" t="n">
         <v>7.6</v>
@@ -2553,13 +2620,13 @@
         <v>21.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.5</v>
+        <v>103.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2571,7 +2638,7 @@
         <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>9</v>
@@ -2589,19 +2656,19 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
         <v>13</v>
       </c>
       <c r="AP12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ12" t="n">
         <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2616,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
@@ -2634,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E13" t="n">
         <v>21</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>0.309</v>
+        <v>0.313</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="J13" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L13" t="n">
         <v>4.3</v>
@@ -2693,31 +2760,31 @@
         <v>13.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>0.325</v>
       </c>
       <c r="O13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="P13" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="Q13" t="n">
         <v>0.784</v>
       </c>
       <c r="R13" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S13" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T13" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U13" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V13" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2735,13 +2802,13 @@
         <v>22</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC13" t="n">
         <v>-6.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,7 +2820,7 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
@@ -2762,7 +2829,7 @@
         <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL13" t="n">
         <v>28</v>
@@ -2774,10 +2841,10 @@
         <v>29</v>
       </c>
       <c r="AO13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
@@ -2816,7 +2883,7 @@
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -2845,46 +2912,46 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F14" t="n">
         <v>21</v>
       </c>
       <c r="G14" t="n">
-        <v>0.696</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39.6</v>
+        <v>39.4</v>
       </c>
       <c r="J14" t="n">
         <v>82.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M14" t="n">
         <v>20.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="O14" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="P14" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R14" t="n">
         <v>10.8</v>
@@ -2893,10 +2960,10 @@
         <v>33.2</v>
       </c>
       <c r="T14" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U14" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
         <v>14.3</v>
@@ -2905,25 +2972,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
         <v>20.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.1</v>
+        <v>107.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2935,13 +3002,13 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
@@ -2953,7 +3020,7 @@
         <v>7</v>
       </c>
       <c r="AN14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2992,7 +3059,7 @@
         <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
         <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>0.25</v>
+        <v>0.239</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
@@ -3048,31 +3115,31 @@
         <v>81.59999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L15" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M15" t="n">
         <v>21.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="O15" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P15" t="n">
         <v>25.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.731</v>
+        <v>0.729</v>
       </c>
       <c r="R15" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S15" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T15" t="n">
         <v>41.6</v>
@@ -3081,10 +3148,10 @@
         <v>19.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W15" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="X15" t="n">
         <v>4.9</v>
@@ -3093,34 +3160,34 @@
         <v>4.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA15" t="n">
         <v>22.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-6.5</v>
       </c>
       <c r="AD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH15" t="n">
         <v>15</v>
       </c>
-      <c r="AE15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>16</v>
-      </c>
       <c r="AI15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ15" t="n">
         <v>13</v>
@@ -3135,7 +3202,7 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
         <v>17</v>
@@ -3144,7 +3211,7 @@
         <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
@@ -3156,22 +3223,22 @@
         <v>17</v>
       </c>
       <c r="AU15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV15" t="n">
         <v>28</v>
       </c>
       <c r="AW15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX15" t="n">
         <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA15" t="n">
         <v>7</v>
@@ -3180,7 +3247,7 @@
         <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -3209,64 +3276,64 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" t="n">
         <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16" t="n">
-        <v>0.176</v>
+        <v>0.179</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J16" t="n">
-        <v>77.8</v>
+        <v>78</v>
       </c>
       <c r="K16" t="n">
         <v>0.453</v>
       </c>
       <c r="L16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M16" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="N16" t="n">
         <v>0.35</v>
       </c>
       <c r="O16" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q16" t="n">
         <v>0.72</v>
       </c>
       <c r="R16" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>28.8</v>
       </c>
       <c r="T16" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="U16" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V16" t="n">
         <v>14.9</v>
       </c>
       <c r="W16" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X16" t="n">
         <v>4.2</v>
@@ -3281,13 +3348,13 @@
         <v>20.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>93</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI16" t="n">
         <v>28</v>
@@ -3317,7 +3384,7 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>25</v>
@@ -3326,7 +3393,7 @@
         <v>22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3341,7 +3408,7 @@
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW16" t="n">
         <v>19</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3487,10 +3554,10 @@
         <v>18</v>
       </c>
       <c r="AJ17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
@@ -3502,7 +3569,7 @@
         <v>26</v>
       </c>
       <c r="AO17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP17" t="n">
         <v>21</v>
@@ -3520,19 +3587,19 @@
         <v>22</v>
       </c>
       <c r="AU17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
         <v>23</v>
       </c>
       <c r="AX17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY17" t="n">
         <v>20</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>21</v>
       </c>
       <c r="AZ17" t="n">
         <v>20</v>
@@ -3544,7 +3611,7 @@
         <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -3573,58 +3640,58 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>0.25</v>
+        <v>0.254</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
       </c>
       <c r="I18" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J18" t="n">
         <v>82.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.448</v>
+        <v>0.446</v>
       </c>
       <c r="L18" t="n">
         <v>5.3</v>
       </c>
       <c r="M18" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O18" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P18" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0.73</v>
       </c>
       <c r="R18" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S18" t="n">
         <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U18" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V18" t="n">
         <v>15</v>
@@ -3633,7 +3700,7 @@
         <v>7.5</v>
       </c>
       <c r="X18" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Y18" t="n">
         <v>5.9</v>
@@ -3645,13 +3712,13 @@
         <v>17.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.5</v>
+        <v>94.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6.9</v>
+        <v>-6.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
@@ -3669,10 +3736,10 @@
         <v>12</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
         <v>25</v>
@@ -3690,22 +3757,22 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU18" t="n">
         <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW18" t="n">
         <v>12</v>
@@ -3717,7 +3784,7 @@
         <v>29</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -3755,64 +3822,64 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19" t="n">
         <v>29</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>0.42</v>
+        <v>0.426</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="J19" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L19" t="n">
         <v>5.8</v>
       </c>
       <c r="M19" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O19" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="P19" t="n">
         <v>27.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.729</v>
+        <v>0.728</v>
       </c>
       <c r="R19" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S19" t="n">
         <v>30.8</v>
       </c>
       <c r="T19" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U19" t="n">
         <v>23.3</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W19" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X19" t="n">
         <v>4.7</v>
@@ -3827,25 +3894,25 @@
         <v>22.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.2</v>
+        <v>-5.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
         <v>29</v>
@@ -3860,10 +3927,10 @@
         <v>20</v>
       </c>
       <c r="AM19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3884,10 +3951,10 @@
         <v>12</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -4015,10 +4082,10 @@
         <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF20" t="n">
         <v>3</v>
@@ -4072,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
         <v>28</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC20" t="n">
         <v>5</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E21" t="n">
         <v>19</v>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
-        <v>0.279</v>
+        <v>0.284</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J21" t="n">
-        <v>80.7</v>
+        <v>80.5</v>
       </c>
       <c r="K21" t="n">
         <v>0.438</v>
@@ -4149,7 +4216,7 @@
         <v>17.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.335</v>
+        <v>0.336</v>
       </c>
       <c r="O21" t="n">
         <v>18.9</v>
@@ -4158,28 +4225,28 @@
         <v>26.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.726</v>
+        <v>0.724</v>
       </c>
       <c r="R21" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S21" t="n">
         <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U21" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="V21" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W21" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Y21" t="n">
         <v>5.2</v>
@@ -4188,16 +4255,16 @@
         <v>21.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4218,7 +4285,7 @@
         <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
         <v>21</v>
@@ -4251,10 +4318,10 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4266,13 +4333,13 @@
         <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB21" t="n">
         <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E22" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
         <v>25</v>
       </c>
       <c r="G22" t="n">
-        <v>0.648</v>
+        <v>0.643</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4325,37 +4392,37 @@
         <v>0.474</v>
       </c>
       <c r="L22" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M22" t="n">
         <v>25</v>
       </c>
       <c r="N22" t="n">
-        <v>0.386</v>
+        <v>0.383</v>
       </c>
       <c r="O22" t="n">
         <v>20.8</v>
       </c>
       <c r="P22" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.728</v>
+        <v>0.726</v>
       </c>
       <c r="R22" t="n">
         <v>9.5</v>
       </c>
       <c r="S22" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T22" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U22" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V22" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W22" t="n">
         <v>6.1</v>
@@ -4373,16 +4440,16 @@
         <v>23.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.9</v>
+        <v>104.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF22" t="n">
         <v>8</v>
@@ -4400,7 +4467,7 @@
         <v>26</v>
       </c>
       <c r="AK22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL22" t="n">
         <v>1</v>
@@ -4433,7 +4500,7 @@
         <v>22</v>
       </c>
       <c r="AV22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW22" t="n">
         <v>28</v>
@@ -4442,7 +4509,7 @@
         <v>25</v>
       </c>
       <c r="AY22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
         <v>11</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E23" t="n">
         <v>34</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,13 +4568,13 @@
         <v>37.4</v>
       </c>
       <c r="J23" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K23" t="n">
         <v>0.461</v>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M23" t="n">
         <v>11.1</v>
@@ -4516,19 +4583,19 @@
         <v>0.319</v>
       </c>
       <c r="O23" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P23" t="n">
         <v>26</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.705</v>
+        <v>0.707</v>
       </c>
       <c r="R23" t="n">
         <v>13.1</v>
       </c>
       <c r="S23" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="T23" t="n">
         <v>42</v>
@@ -4558,13 +4625,13 @@
         <v>96.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF23" t="n">
         <v>17</v>
@@ -4573,7 +4640,7 @@
         <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4627,13 +4694,13 @@
         <v>15</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -4743,19 +4810,19 @@
         <v>5.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF24" t="n">
         <v>5</v>
       </c>
       <c r="AG24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4788,7 +4855,7 @@
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT24" t="n">
         <v>20</v>
@@ -4806,7 +4873,7 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ24" t="n">
         <v>8</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F25" t="n">
         <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>0.522</v>
+        <v>0.515</v>
       </c>
       <c r="H25" t="n">
         <v>48.7</v>
@@ -4865,10 +4932,10 @@
         <v>35.8</v>
       </c>
       <c r="J25" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L25" t="n">
         <v>6.4</v>
@@ -4877,13 +4944,13 @@
         <v>17.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O25" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P25" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q25" t="n">
         <v>0.767</v>
@@ -4895,10 +4962,10 @@
         <v>29.6</v>
       </c>
       <c r="T25" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U25" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V25" t="n">
         <v>13.1</v>
@@ -4919,13 +4986,13 @@
         <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4955,7 +5022,7 @@
         <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
         <v>22</v>
@@ -4970,13 +5037,13 @@
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
         <v>27</v>
       </c>
       <c r="AU25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV25" t="n">
         <v>6</v>
@@ -4985,10 +5052,10 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ25" t="n">
         <v>9</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -5029,40 +5096,40 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E26" t="n">
         <v>31</v>
       </c>
       <c r="F26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G26" t="n">
-        <v>0.456</v>
+        <v>0.463</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L26" t="n">
         <v>6.2</v>
       </c>
       <c r="M26" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="N26" t="n">
         <v>0.371</v>
       </c>
       <c r="O26" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="P26" t="n">
         <v>27.8</v>
@@ -5071,19 +5138,19 @@
         <v>0.794</v>
       </c>
       <c r="R26" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S26" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T26" t="n">
         <v>40.4</v>
       </c>
       <c r="U26" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="V26" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W26" t="n">
         <v>7.8</v>
@@ -5101,13 +5168,13 @@
         <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>101.7</v>
+        <v>101.9</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,16 +5186,16 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI26" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AJ26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
         <v>17</v>
@@ -5167,7 +5234,7 @@
         <v>8</v>
       </c>
       <c r="AX26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY26" t="n">
         <v>27</v>
@@ -5182,7 +5249,7 @@
         <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -5211,58 +5278,58 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E27" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F27" t="n">
         <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.667</v>
+        <v>0.662</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
       </c>
       <c r="I27" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J27" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L27" t="n">
         <v>7.6</v>
       </c>
       <c r="M27" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="O27" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P27" t="n">
         <v>22</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R27" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T27" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U27" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V27" t="n">
         <v>12.8</v>
@@ -5283,16 +5350,16 @@
         <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>95.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF27" t="n">
         <v>7</v>
@@ -5301,7 +5368,7 @@
         <v>7</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5319,7 +5386,7 @@
         <v>8</v>
       </c>
       <c r="AN27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G28" t="n">
-        <v>0.232</v>
+        <v>0.235</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5411,7 +5478,7 @@
         <v>38</v>
       </c>
       <c r="J28" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K28" t="n">
         <v>0.445</v>
@@ -5435,10 +5502,10 @@
         <v>0.767</v>
       </c>
       <c r="R28" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S28" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="T28" t="n">
         <v>44.7</v>
@@ -5453,28 +5520,28 @@
         <v>6.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AA28" t="n">
         <v>19.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>-9</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF28" t="n">
         <v>29</v>
@@ -5492,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL28" t="n">
         <v>29</v>
@@ -5504,7 +5571,7 @@
         <v>27</v>
       </c>
       <c r="AO28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP28" t="n">
         <v>25</v>
@@ -5513,7 +5580,7 @@
         <v>12</v>
       </c>
       <c r="AR28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5537,7 +5604,7 @@
         <v>26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E29" t="n">
         <v>35</v>
       </c>
       <c r="F29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G29" t="n">
-        <v>0.507</v>
+        <v>0.515</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J29" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L29" t="n">
         <v>7.3</v>
@@ -5605,13 +5672,13 @@
         <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>0.404</v>
+        <v>0.405</v>
       </c>
       <c r="O29" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P29" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="Q29" t="n">
         <v>0.8110000000000001</v>
@@ -5620,10 +5687,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="U29" t="n">
         <v>23.3</v>
@@ -5641,31 +5708,31 @@
         <v>4.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>100</v>
+        <v>100.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5674,7 +5741,7 @@
         <v>10</v>
       </c>
       <c r="AK29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5704,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
@@ -5719,13 +5786,13 @@
         <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>5.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
       </c>
       <c r="AG30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH30" t="n">
         <v>30</v>
@@ -5865,7 +5932,7 @@
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5877,7 +5944,7 @@
         <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS30" t="n">
         <v>26</v>
@@ -5889,7 +5956,7 @@
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
@@ -5939,58 +6006,58 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F31" t="n">
         <v>33</v>
       </c>
       <c r="G31" t="n">
-        <v>0.515</v>
+        <v>0.507</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J31" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L31" t="n">
         <v>6.6</v>
       </c>
       <c r="M31" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O31" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="P31" t="n">
         <v>24.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.786</v>
+        <v>0.789</v>
       </c>
       <c r="R31" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S31" t="n">
         <v>29.6</v>
       </c>
       <c r="T31" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U31" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="V31" t="n">
         <v>13.4</v>
@@ -6014,25 +6081,25 @@
         <v>98.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF31" t="n">
         <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH31" t="n">
         <v>2</v>
       </c>
       <c r="AI31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="n">
         <v>11</v>
@@ -6047,22 +6114,22 @@
         <v>11</v>
       </c>
       <c r="AN31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
       </c>
       <c r="AP31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ31" t="n">
         <v>4</v>
       </c>
       <c r="AR31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT31" t="n">
         <v>15</v>
@@ -6083,7 +6150,7 @@
         <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA31" t="n">
         <v>22</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-21-2007-08</t>
+          <t>2008-03-21</t>
         </is>
       </c>
     </row>
